--- a/chapters/06/python_analytics/AIHE-PY11_roi_net_benefit_and_benefit_realization_analysis/data/xlsx/11_roi_benefit_realization_sample.xlsx
+++ b/chapters/06/python_analytics/AIHE-PY11_roi_net_benefit_and_benefit_realization_analysis/data/xlsx/11_roi_benefit_realization_sample.xlsx
@@ -83,7 +83,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,7 +91,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,10 +121,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,10 +132,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
